--- a/output/pdf_financials_xlsx/OOR.xlsx
+++ b/output/pdf_financials_xlsx/OOR.xlsx
@@ -3383,28 +3383,28 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.401169</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.468018</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.5036580000000001</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.532645</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.565979</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.18569</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.18569</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.18569</v>
       </c>
     </row>
     <row r="93">
@@ -5588,7 +5588,11 @@
           <t>Share-based payments reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -6230,7 +6234,11 @@
           <t>Share-based payments reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" s="5" t="n">
         <v>0.401169</v>
       </c>

--- a/output/pdf_financials_xlsx/OOR.xlsx
+++ b/output/pdf_financials_xlsx/OOR.xlsx
@@ -759,13 +759,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.011209</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.004288</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.002142</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1268,13 +1268,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.46683</v>
+        <v>-0.478039</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.981355</v>
+        <v>-0.985643</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.6642400000000001</v>
+        <v>-0.666382</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-0.253051</v>
@@ -1330,13 +1330,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.46683</v>
+        <v>-0.478039</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.981355</v>
+        <v>-0.985643</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.6642400000000001</v>
+        <v>-0.666382</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-0.253051</v>
@@ -1493,28 +1493,28 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.882537</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.393165</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.169342</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.932497</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.07219200000000001</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.436992</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.03353</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.164591</v>
       </c>
     </row>
     <row r="35">
@@ -1555,28 +1555,28 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.882537</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.393165</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.169342</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.932497</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.07219200000000001</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.436992</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.03353</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.164591</v>
       </c>
     </row>
     <row r="37">
@@ -1927,28 +1927,28 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.889721</v>
+        <v>0.007184</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.396882</v>
+        <v>0.003717</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.173032</v>
+        <v>0.00369</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.936221</v>
+        <v>0.003724</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.075859</v>
+        <v>0.003667</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.442253</v>
+        <v>0.005261</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.039203</v>
+        <v>0.005673</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.174846</v>
+        <v>0.010255</v>
       </c>
     </row>
     <row r="49">
@@ -4378,13 +4378,13 @@
         <v>0</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.020285</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-0.022316</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.024544</v>
       </c>
     </row>
     <row r="125">
@@ -4409,13 +4409,13 @@
         <v>0</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.020285</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-0.022316</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.024544</v>
       </c>
     </row>
     <row r="126">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -7374,7 +7374,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -12336,7 +12340,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E141" s="5" t="n">

--- a/output/pdf_financials_xlsx/OOR.xlsx
+++ b/output/pdf_financials_xlsx/OOR.xlsx
@@ -11104,7 +11104,11 @@
           <t>Depreciation of right-of-use asset (Note 8)</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/OOR.xlsx
+++ b/output/pdf_financials_xlsx/OOR.xlsx
@@ -2556,28 +2556,28 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.023625</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.0226</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.034</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.0329</v>
       </c>
     </row>
     <row r="68">
@@ -7160,7 +7160,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
